--- a/DTS-Final Version/outputs/01a13ce9-5764-7a21-9407-956bbec1ab43/DTS-Partial-and-Missing-Features.xlsx
+++ b/DTS-Final Version/outputs/01a13ce9-5764-7a21-9407-956bbec1ab43/DTS-Partial-and-Missing-Features.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\test server\staging-dts\New folder\dts-final version-workflow\DTS-Final Version\outputs\01a13ce9-5764-7a21-9407-956bbec1ab43\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7493D81-32CE-4119-9C2B-A211C319555C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2895059-5C16-479C-8E79-17B5E359F75D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1211" uniqueCount="917">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1296" uniqueCount="923">
   <si>
     <t>DTS partial features</t>
   </si>
@@ -2772,13 +2772,31 @@
   </si>
   <si>
     <t>discuss first before adding this</t>
+  </si>
+  <si>
+    <t>discuss archive architecture</t>
+  </si>
+  <si>
+    <t>explain this</t>
+  </si>
+  <si>
+    <t>not needed for now</t>
+  </si>
+  <si>
+    <t>uses google drive</t>
+  </si>
+  <si>
+    <t>disregard</t>
+  </si>
+  <si>
+    <t>I think this was implemented already</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -2822,6 +2840,12 @@
       <sz val="10"/>
       <color rgb="FFA4262C"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF202936"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="6">
@@ -2989,16 +3013,16 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3075,7 +3099,7 @@
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Category"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Roadmap requirement"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Existing behavior / remaining gap"/>
-    <tableColumn id="5" xr3:uid="{ED78F07D-E607-4267-A986-52F2708309E0}" name="Remarks" dataDxfId="0"/>
+    <tableColumn id="5" xr3:uid="{ED78F07D-E607-4267-A986-52F2708309E0}" name="Remarks" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3089,7 +3113,7 @@
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Category"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Roadmap requirement"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Existing behavior / remaining gap"/>
-    <tableColumn id="5" xr3:uid="{F7888078-5CEB-4123-9593-9FF0BFCB3727}" name="Remarks" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{F7888078-5CEB-4123-9593-9FF0BFCB3727}" name="Remarks" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3369,7 +3393,7 @@
       <c r="D7" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="E7" s="24"/>
+      <c r="E7" s="10"/>
     </row>
     <row r="8" spans="1:5" ht="39.950000000000003" customHeight="1">
       <c r="A8" s="13" t="s">
@@ -3474,7 +3498,7 @@
       <c r="D14" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="E14" s="25"/>
+      <c r="E14" s="14"/>
     </row>
     <row r="15" spans="1:5" ht="54.95" customHeight="1">
       <c r="A15" s="9" t="s">
@@ -3549,7 +3573,7 @@
       <c r="D19" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="E19" s="24"/>
+      <c r="E19" s="10"/>
     </row>
     <row r="20" spans="1:5" ht="36.950000000000003" customHeight="1">
       <c r="A20" s="13" t="s">
@@ -3699,7 +3723,7 @@
       <c r="D29" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="E29" s="24"/>
+      <c r="E29" s="10"/>
     </row>
     <row r="30" spans="1:5" ht="36.950000000000003" customHeight="1">
       <c r="A30" s="13" t="s">
@@ -3819,7 +3843,7 @@
       <c r="D37" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="E37" s="24"/>
+      <c r="E37" s="10"/>
     </row>
     <row r="38" spans="1:5" ht="39.950000000000003" customHeight="1">
       <c r="A38" s="13" t="s">
@@ -3879,7 +3903,7 @@
       <c r="D41" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="E41" s="24"/>
+      <c r="E41" s="10"/>
     </row>
     <row r="42" spans="1:5" ht="39.950000000000003" customHeight="1">
       <c r="A42" s="13" t="s">
@@ -4044,7 +4068,7 @@
       <c r="D52" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="E52" s="25"/>
+      <c r="E52" s="14"/>
     </row>
     <row r="53" spans="1:5" ht="39.950000000000003" customHeight="1">
       <c r="A53" s="9" t="s">
@@ -4194,7 +4218,7 @@
       <c r="D62" s="16" t="s">
         <v>182</v>
       </c>
-      <c r="E62" s="25"/>
+      <c r="E62" s="14"/>
     </row>
     <row r="63" spans="1:5" ht="39.950000000000003" customHeight="1">
       <c r="A63" s="9" t="s">
@@ -4269,7 +4293,7 @@
       <c r="D67" s="12" t="s">
         <v>198</v>
       </c>
-      <c r="E67" s="24"/>
+      <c r="E67" s="10"/>
     </row>
     <row r="68" spans="1:5" ht="39.950000000000003" customHeight="1">
       <c r="A68" s="13" t="s">
@@ -4344,7 +4368,7 @@
       <c r="D72" s="16" t="s">
         <v>214</v>
       </c>
-      <c r="E72" s="25"/>
+      <c r="E72" s="14"/>
     </row>
     <row r="73" spans="1:5" ht="39.950000000000003" customHeight="1">
       <c r="A73" s="9" t="s">
@@ -4449,7 +4473,7 @@
       <c r="D79" s="12" t="s">
         <v>236</v>
       </c>
-      <c r="E79" s="24"/>
+      <c r="E79" s="10"/>
     </row>
     <row r="80" spans="1:5" ht="36.950000000000003" customHeight="1">
       <c r="A80" s="13" t="s">
@@ -4554,7 +4578,7 @@
       <c r="D86" s="16" t="s">
         <v>258</v>
       </c>
-      <c r="E86" s="25"/>
+      <c r="E86" s="14"/>
     </row>
     <row r="87" spans="1:5" ht="39.950000000000003" customHeight="1">
       <c r="A87" s="9" t="s">
@@ -4809,7 +4833,7 @@
       <c r="D103" s="12" t="s">
         <v>310</v>
       </c>
-      <c r="E103" s="24"/>
+      <c r="E103" s="10"/>
     </row>
     <row r="104" spans="1:5" ht="39.950000000000003" customHeight="1">
       <c r="A104" s="13" t="s">
@@ -4929,7 +4953,7 @@
       <c r="D111" s="12" t="s">
         <v>335</v>
       </c>
-      <c r="E111" s="24"/>
+      <c r="E111" s="10"/>
     </row>
     <row r="112" spans="1:5" ht="39.950000000000003" customHeight="1">
       <c r="A112" s="13" t="s">
@@ -5004,7 +5028,7 @@
       <c r="D116" s="16" t="s">
         <v>351</v>
       </c>
-      <c r="E116" s="25"/>
+      <c r="E116" s="14"/>
     </row>
     <row r="117" spans="1:5" ht="39.950000000000003" customHeight="1">
       <c r="A117" s="9" t="s">
@@ -5094,7 +5118,7 @@
       <c r="D122" s="16" t="s">
         <v>370</v>
       </c>
-      <c r="E122" s="25"/>
+      <c r="E122" s="14"/>
     </row>
     <row r="123" spans="1:5" ht="39.950000000000003" customHeight="1">
       <c r="A123" s="9" t="s">
@@ -5274,7 +5298,7 @@
       <c r="D134" s="16" t="s">
         <v>407</v>
       </c>
-      <c r="E134" s="25"/>
+      <c r="E134" s="14"/>
     </row>
     <row r="135" spans="1:5" ht="39.950000000000003" customHeight="1">
       <c r="A135" s="9" t="s">
@@ -5334,7 +5358,7 @@
       <c r="D138" s="16" t="s">
         <v>420</v>
       </c>
-      <c r="E138" s="25"/>
+      <c r="E138" s="14"/>
     </row>
     <row r="139" spans="1:5" ht="39.950000000000003" customHeight="1">
       <c r="A139" s="9" t="s">
@@ -5592,7 +5616,7 @@
       <c r="D154" s="14" t="s">
         <v>470</v>
       </c>
-      <c r="E154" s="26" t="s">
+      <c r="E154" s="24" t="s">
         <v>913</v>
       </c>
     </row>
@@ -5796,7 +5820,7 @@
       <c r="D166" s="16" t="s">
         <v>509</v>
       </c>
-      <c r="E166" s="25"/>
+      <c r="E166" s="14"/>
     </row>
     <row r="167" spans="1:5" ht="39.950000000000003" customHeight="1">
       <c r="A167" s="9" t="s">
@@ -6037,7 +6061,7 @@
       <c r="D7" s="12" t="s">
         <v>545</v>
       </c>
-      <c r="E7" s="24"/>
+      <c r="E7" s="10"/>
     </row>
     <row r="8" spans="1:5" ht="36.950000000000003" customHeight="1">
       <c r="A8" s="21" t="s">
@@ -6187,7 +6211,7 @@
       <c r="D17" s="12" t="s">
         <v>575</v>
       </c>
-      <c r="E17" s="24"/>
+      <c r="E17" s="10"/>
     </row>
     <row r="18" spans="1:5" ht="36.950000000000003" customHeight="1">
       <c r="A18" s="21" t="s">
@@ -6217,7 +6241,7 @@
       <c r="D19" s="12" t="s">
         <v>581</v>
       </c>
-      <c r="E19" s="24" t="s">
+      <c r="E19" s="10" t="s">
         <v>915</v>
       </c>
     </row>
@@ -6379,7 +6403,7 @@
       <c r="D29" s="12" t="s">
         <v>611</v>
       </c>
-      <c r="E29" s="24"/>
+      <c r="E29" s="10"/>
     </row>
     <row r="30" spans="1:5" ht="39.950000000000003" customHeight="1">
       <c r="A30" s="21" t="s">
@@ -6439,7 +6463,7 @@
       <c r="D33" s="12" t="s">
         <v>623</v>
       </c>
-      <c r="E33" s="24"/>
+      <c r="E33" s="10"/>
     </row>
     <row r="34" spans="1:5" ht="39.950000000000003" customHeight="1">
       <c r="A34" s="21" t="s">
@@ -6604,7 +6628,9 @@
       <c r="D44" s="14" t="s">
         <v>655</v>
       </c>
-      <c r="E44" s="14"/>
+      <c r="E44" s="14" t="s">
+        <v>916</v>
+      </c>
     </row>
     <row r="45" spans="1:5" ht="39.950000000000003" customHeight="1">
       <c r="A45" s="19" t="s">
@@ -6619,7 +6645,9 @@
       <c r="D45" s="10" t="s">
         <v>658</v>
       </c>
-      <c r="E45" s="10"/>
+      <c r="E45" s="14" t="s">
+        <v>916</v>
+      </c>
     </row>
     <row r="46" spans="1:5" ht="39.950000000000003" customHeight="1">
       <c r="A46" s="22" t="s">
@@ -6634,7 +6662,9 @@
       <c r="D46" s="16" t="s">
         <v>661</v>
       </c>
-      <c r="E46" s="25"/>
+      <c r="E46" s="26" t="s">
+        <v>921</v>
+      </c>
     </row>
     <row r="47" spans="1:5" ht="39.950000000000003" customHeight="1">
       <c r="A47" s="19" t="s">
@@ -6649,7 +6679,9 @@
       <c r="D47" s="10" t="s">
         <v>664</v>
       </c>
-      <c r="E47" s="10"/>
+      <c r="E47" s="26" t="s">
+        <v>921</v>
+      </c>
     </row>
     <row r="48" spans="1:5" ht="39.950000000000003" customHeight="1">
       <c r="A48" s="21" t="s">
@@ -6664,7 +6696,9 @@
       <c r="D48" s="14" t="s">
         <v>667</v>
       </c>
-      <c r="E48" s="14"/>
+      <c r="E48" s="26" t="s">
+        <v>921</v>
+      </c>
     </row>
     <row r="49" spans="1:5" ht="39.950000000000003" customHeight="1">
       <c r="A49" s="19" t="s">
@@ -6679,7 +6713,9 @@
       <c r="D49" s="10" t="s">
         <v>670</v>
       </c>
-      <c r="E49" s="10"/>
+      <c r="E49" s="26" t="s">
+        <v>921</v>
+      </c>
     </row>
     <row r="50" spans="1:5" ht="39.950000000000003" customHeight="1">
       <c r="A50" s="22" t="s">
@@ -6694,7 +6730,9 @@
       <c r="D50" s="16" t="s">
         <v>673</v>
       </c>
-      <c r="E50" s="25"/>
+      <c r="E50" s="26" t="s">
+        <v>921</v>
+      </c>
     </row>
     <row r="51" spans="1:5" ht="39.950000000000003" customHeight="1">
       <c r="A51" s="19" t="s">
@@ -6709,7 +6747,9 @@
       <c r="D51" s="10" t="s">
         <v>676</v>
       </c>
-      <c r="E51" s="10"/>
+      <c r="E51" s="26" t="s">
+        <v>921</v>
+      </c>
     </row>
     <row r="52" spans="1:5" ht="39.950000000000003" customHeight="1">
       <c r="A52" s="21" t="s">
@@ -6724,7 +6764,9 @@
       <c r="D52" s="14" t="s">
         <v>679</v>
       </c>
-      <c r="E52" s="14"/>
+      <c r="E52" s="26" t="s">
+        <v>921</v>
+      </c>
     </row>
     <row r="53" spans="1:5" ht="39.950000000000003" customHeight="1">
       <c r="A53" s="19" t="s">
@@ -6739,7 +6781,9 @@
       <c r="D53" s="10" t="s">
         <v>682</v>
       </c>
-      <c r="E53" s="10"/>
+      <c r="E53" s="14" t="s">
+        <v>916</v>
+      </c>
     </row>
     <row r="54" spans="1:5" ht="39.950000000000003" customHeight="1">
       <c r="A54" s="21" t="s">
@@ -6754,7 +6798,9 @@
       <c r="D54" s="14" t="s">
         <v>685</v>
       </c>
-      <c r="E54" s="14"/>
+      <c r="E54" s="26" t="s">
+        <v>921</v>
+      </c>
     </row>
     <row r="55" spans="1:5" ht="36.950000000000003" customHeight="1">
       <c r="A55" s="20" t="s">
@@ -6769,7 +6815,9 @@
       <c r="D55" s="12" t="s">
         <v>688</v>
       </c>
-      <c r="E55" s="24"/>
+      <c r="E55" s="14" t="s">
+        <v>916</v>
+      </c>
     </row>
     <row r="56" spans="1:5" ht="36.950000000000003" customHeight="1">
       <c r="A56" s="21" t="s">
@@ -6784,7 +6832,9 @@
       <c r="D56" s="14" t="s">
         <v>691</v>
       </c>
-      <c r="E56" s="14"/>
+      <c r="E56" s="14" t="s">
+        <v>916</v>
+      </c>
     </row>
     <row r="57" spans="1:5" ht="36.950000000000003" customHeight="1">
       <c r="A57" s="19" t="s">
@@ -6799,7 +6849,9 @@
       <c r="D57" s="10" t="s">
         <v>694</v>
       </c>
-      <c r="E57" s="10"/>
+      <c r="E57" s="26" t="s">
+        <v>921</v>
+      </c>
     </row>
     <row r="58" spans="1:5" ht="36.950000000000003" customHeight="1">
       <c r="A58" s="21" t="s">
@@ -6814,7 +6866,9 @@
       <c r="D58" s="14" t="s">
         <v>697</v>
       </c>
-      <c r="E58" s="14"/>
+      <c r="E58" s="26" t="s">
+        <v>921</v>
+      </c>
     </row>
     <row r="59" spans="1:5" ht="36.950000000000003" customHeight="1">
       <c r="A59" s="19" t="s">
@@ -6829,7 +6883,9 @@
       <c r="D59" s="10" t="s">
         <v>700</v>
       </c>
-      <c r="E59" s="10"/>
+      <c r="E59" s="26" t="s">
+        <v>922</v>
+      </c>
     </row>
     <row r="60" spans="1:5" ht="36.950000000000003" customHeight="1">
       <c r="A60" s="21" t="s">
@@ -6844,7 +6900,9 @@
       <c r="D60" s="14" t="s">
         <v>703</v>
       </c>
-      <c r="E60" s="14"/>
+      <c r="E60" s="14" t="s">
+        <v>916</v>
+      </c>
     </row>
     <row r="61" spans="1:5" ht="36.950000000000003" customHeight="1">
       <c r="A61" s="19" t="s">
@@ -6859,7 +6917,9 @@
       <c r="D61" s="10" t="s">
         <v>706</v>
       </c>
-      <c r="E61" s="10"/>
+      <c r="E61" s="14" t="s">
+        <v>916</v>
+      </c>
     </row>
     <row r="62" spans="1:5" ht="36.950000000000003" customHeight="1">
       <c r="A62" s="21" t="s">
@@ -6874,7 +6934,9 @@
       <c r="D62" s="14" t="s">
         <v>709</v>
       </c>
-      <c r="E62" s="14"/>
+      <c r="E62" s="14" t="s">
+        <v>916</v>
+      </c>
     </row>
     <row r="63" spans="1:5" ht="39.950000000000003" customHeight="1">
       <c r="A63" s="19" t="s">
@@ -6889,7 +6951,9 @@
       <c r="D63" s="10" t="s">
         <v>712</v>
       </c>
-      <c r="E63" s="10"/>
+      <c r="E63" s="26" t="s">
+        <v>921</v>
+      </c>
     </row>
     <row r="64" spans="1:5" ht="36.950000000000003" customHeight="1">
       <c r="A64" s="22" t="s">
@@ -6904,7 +6968,9 @@
       <c r="D64" s="16" t="s">
         <v>715</v>
       </c>
-      <c r="E64" s="25"/>
+      <c r="E64" s="14" t="s">
+        <v>916</v>
+      </c>
     </row>
     <row r="65" spans="1:5" ht="39.950000000000003" customHeight="1">
       <c r="A65" s="19" t="s">
@@ -6919,7 +6985,9 @@
       <c r="D65" s="10" t="s">
         <v>718</v>
       </c>
-      <c r="E65" s="10"/>
+      <c r="E65" s="26" t="s">
+        <v>921</v>
+      </c>
     </row>
     <row r="66" spans="1:5" ht="36.950000000000003" customHeight="1">
       <c r="A66" s="21" t="s">
@@ -6934,7 +7002,9 @@
       <c r="D66" s="14" t="s">
         <v>721</v>
       </c>
-      <c r="E66" s="14"/>
+      <c r="E66" s="14" t="s">
+        <v>916</v>
+      </c>
     </row>
     <row r="67" spans="1:5" ht="36.950000000000003" customHeight="1">
       <c r="A67" s="19" t="s">
@@ -6949,7 +7019,9 @@
       <c r="D67" s="10" t="s">
         <v>724</v>
       </c>
-      <c r="E67" s="10"/>
+      <c r="E67" s="14" t="s">
+        <v>916</v>
+      </c>
     </row>
     <row r="68" spans="1:5" ht="39.950000000000003" customHeight="1">
       <c r="A68" s="22" t="s">
@@ -6964,7 +7036,9 @@
       <c r="D68" s="16" t="s">
         <v>727</v>
       </c>
-      <c r="E68" s="25"/>
+      <c r="E68" s="14" t="s">
+        <v>916</v>
+      </c>
     </row>
     <row r="69" spans="1:5" ht="39.950000000000003" customHeight="1">
       <c r="A69" s="19" t="s">
@@ -6979,7 +7053,9 @@
       <c r="D69" s="10" t="s">
         <v>730</v>
       </c>
-      <c r="E69" s="10"/>
+      <c r="E69" s="14" t="s">
+        <v>916</v>
+      </c>
     </row>
     <row r="70" spans="1:5" ht="39.950000000000003" customHeight="1">
       <c r="A70" s="21" t="s">
@@ -6994,7 +7070,9 @@
       <c r="D70" s="14" t="s">
         <v>733</v>
       </c>
-      <c r="E70" s="14"/>
+      <c r="E70" s="14" t="s">
+        <v>916</v>
+      </c>
     </row>
     <row r="71" spans="1:5" ht="39.950000000000003" customHeight="1">
       <c r="A71" s="19" t="s">
@@ -7009,7 +7087,9 @@
       <c r="D71" s="10" t="s">
         <v>736</v>
       </c>
-      <c r="E71" s="10"/>
+      <c r="E71" s="14" t="s">
+        <v>916</v>
+      </c>
     </row>
     <row r="72" spans="1:5" ht="39.950000000000003" customHeight="1">
       <c r="A72" s="21" t="s">
@@ -7024,7 +7104,9 @@
       <c r="D72" s="14" t="s">
         <v>739</v>
       </c>
-      <c r="E72" s="14"/>
+      <c r="E72" s="26" t="s">
+        <v>921</v>
+      </c>
     </row>
     <row r="73" spans="1:5" ht="39.950000000000003" customHeight="1">
       <c r="A73" s="19" t="s">
@@ -7039,7 +7121,9 @@
       <c r="D73" s="10" t="s">
         <v>742</v>
       </c>
-      <c r="E73" s="10"/>
+      <c r="E73" s="14" t="s">
+        <v>916</v>
+      </c>
     </row>
     <row r="74" spans="1:5" ht="39.950000000000003" customHeight="1">
       <c r="A74" s="21" t="s">
@@ -7054,7 +7138,9 @@
       <c r="D74" s="14" t="s">
         <v>745</v>
       </c>
-      <c r="E74" s="14"/>
+      <c r="E74" s="26" t="s">
+        <v>921</v>
+      </c>
     </row>
     <row r="75" spans="1:5" ht="39.950000000000003" customHeight="1">
       <c r="A75" s="19" t="s">
@@ -7069,7 +7155,9 @@
       <c r="D75" s="10" t="s">
         <v>748</v>
       </c>
-      <c r="E75" s="10"/>
+      <c r="E75" s="26" t="s">
+        <v>921</v>
+      </c>
     </row>
     <row r="76" spans="1:5" ht="36.950000000000003" customHeight="1">
       <c r="A76" s="22" t="s">
@@ -7084,7 +7172,9 @@
       <c r="D76" s="16" t="s">
         <v>751</v>
       </c>
-      <c r="E76" s="25"/>
+      <c r="E76" s="25" t="s">
+        <v>914</v>
+      </c>
     </row>
     <row r="77" spans="1:5" ht="39.950000000000003" customHeight="1">
       <c r="A77" s="20" t="s">
@@ -7099,7 +7189,9 @@
       <c r="D77" s="12" t="s">
         <v>754</v>
       </c>
-      <c r="E77" s="24"/>
+      <c r="E77" s="25" t="s">
+        <v>920</v>
+      </c>
     </row>
     <row r="78" spans="1:5" ht="39.950000000000003" customHeight="1">
       <c r="A78" s="21" t="s">
@@ -7114,7 +7206,9 @@
       <c r="D78" s="14" t="s">
         <v>757</v>
       </c>
-      <c r="E78" s="14"/>
+      <c r="E78" s="14" t="s">
+        <v>916</v>
+      </c>
     </row>
     <row r="79" spans="1:5" ht="39.950000000000003" customHeight="1">
       <c r="A79" s="19" t="s">
@@ -7129,7 +7223,9 @@
       <c r="D79" s="10" t="s">
         <v>760</v>
       </c>
-      <c r="E79" s="10"/>
+      <c r="E79" s="14" t="s">
+        <v>916</v>
+      </c>
     </row>
     <row r="80" spans="1:5" ht="39.950000000000003" customHeight="1">
       <c r="A80" s="21" t="s">
@@ -7144,7 +7240,9 @@
       <c r="D80" s="14" t="s">
         <v>763</v>
       </c>
-      <c r="E80" s="14"/>
+      <c r="E80" s="14" t="s">
+        <v>916</v>
+      </c>
     </row>
     <row r="81" spans="1:5" ht="39.950000000000003" customHeight="1">
       <c r="A81" s="19" t="s">
@@ -7159,7 +7257,9 @@
       <c r="D81" s="10" t="s">
         <v>766</v>
       </c>
-      <c r="E81" s="10"/>
+      <c r="E81" s="14" t="s">
+        <v>916</v>
+      </c>
     </row>
     <row r="82" spans="1:5" ht="39.950000000000003" customHeight="1">
       <c r="A82" s="22" t="s">
@@ -7174,7 +7274,9 @@
       <c r="D82" s="16" t="s">
         <v>769</v>
       </c>
-      <c r="E82" s="25"/>
+      <c r="E82" s="25" t="s">
+        <v>920</v>
+      </c>
     </row>
     <row r="83" spans="1:5" ht="39.950000000000003" customHeight="1">
       <c r="A83" s="19" t="s">
@@ -7189,7 +7291,9 @@
       <c r="D83" s="10" t="s">
         <v>772</v>
       </c>
-      <c r="E83" s="10"/>
+      <c r="E83" s="14" t="s">
+        <v>916</v>
+      </c>
     </row>
     <row r="84" spans="1:5" ht="39.950000000000003" customHeight="1">
       <c r="A84" s="21" t="s">
@@ -7204,7 +7308,9 @@
       <c r="D84" s="14" t="s">
         <v>775</v>
       </c>
-      <c r="E84" s="14"/>
+      <c r="E84" s="14" t="s">
+        <v>916</v>
+      </c>
     </row>
     <row r="85" spans="1:5" ht="39.950000000000003" customHeight="1">
       <c r="A85" s="20" t="s">
@@ -7219,7 +7325,9 @@
       <c r="D85" s="12" t="s">
         <v>778</v>
       </c>
-      <c r="E85" s="24"/>
+      <c r="E85" s="14" t="s">
+        <v>916</v>
+      </c>
     </row>
     <row r="86" spans="1:5" ht="39.950000000000003" customHeight="1">
       <c r="A86" s="21" t="s">
@@ -7234,7 +7342,9 @@
       <c r="D86" s="14" t="s">
         <v>781</v>
       </c>
-      <c r="E86" s="14"/>
+      <c r="E86" s="10" t="s">
+        <v>918</v>
+      </c>
     </row>
     <row r="87" spans="1:5" ht="39.950000000000003" customHeight="1">
       <c r="A87" s="19" t="s">
@@ -7249,7 +7359,9 @@
       <c r="D87" s="10" t="s">
         <v>784</v>
       </c>
-      <c r="E87" s="10"/>
+      <c r="E87" s="10" t="s">
+        <v>918</v>
+      </c>
     </row>
     <row r="88" spans="1:5" ht="39.950000000000003" customHeight="1">
       <c r="A88" s="21" t="s">
@@ -7264,7 +7376,9 @@
       <c r="D88" s="14" t="s">
         <v>787</v>
       </c>
-      <c r="E88" s="14"/>
+      <c r="E88" s="10" t="s">
+        <v>918</v>
+      </c>
     </row>
     <row r="89" spans="1:5" ht="39.950000000000003" customHeight="1">
       <c r="A89" s="19" t="s">
@@ -7279,7 +7393,9 @@
       <c r="D89" s="10" t="s">
         <v>790</v>
       </c>
-      <c r="E89" s="10"/>
+      <c r="E89" s="10" t="s">
+        <v>919</v>
+      </c>
     </row>
     <row r="90" spans="1:5" ht="39.950000000000003" customHeight="1">
       <c r="A90" s="21" t="s">
@@ -7294,7 +7410,9 @@
       <c r="D90" s="14" t="s">
         <v>793</v>
       </c>
-      <c r="E90" s="14"/>
+      <c r="E90" s="14" t="s">
+        <v>916</v>
+      </c>
     </row>
     <row r="91" spans="1:5" ht="39.950000000000003" customHeight="1">
       <c r="A91" s="19" t="s">
@@ -7309,7 +7427,9 @@
       <c r="D91" s="10" t="s">
         <v>796</v>
       </c>
-      <c r="E91" s="10"/>
+      <c r="E91" s="14" t="s">
+        <v>916</v>
+      </c>
     </row>
     <row r="92" spans="1:5" ht="39.950000000000003" customHeight="1">
       <c r="A92" s="21" t="s">
@@ -7324,7 +7444,9 @@
       <c r="D92" s="14" t="s">
         <v>799</v>
       </c>
-      <c r="E92" s="14"/>
+      <c r="E92" s="14" t="s">
+        <v>916</v>
+      </c>
     </row>
     <row r="93" spans="1:5" ht="39.950000000000003" customHeight="1">
       <c r="A93" s="19" t="s">
@@ -7339,7 +7461,9 @@
       <c r="D93" s="10" t="s">
         <v>802</v>
       </c>
-      <c r="E93" s="10"/>
+      <c r="E93" s="10" t="s">
+        <v>914</v>
+      </c>
     </row>
     <row r="94" spans="1:5" ht="39.950000000000003" customHeight="1">
       <c r="A94" s="22" t="s">
@@ -7354,7 +7478,9 @@
       <c r="D94" s="16" t="s">
         <v>805</v>
       </c>
-      <c r="E94" s="25"/>
+      <c r="E94" s="14" t="s">
+        <v>916</v>
+      </c>
     </row>
     <row r="95" spans="1:5" ht="39.950000000000003" customHeight="1">
       <c r="A95" s="19" t="s">
@@ -7369,7 +7495,9 @@
       <c r="D95" s="10" t="s">
         <v>808</v>
       </c>
-      <c r="E95" s="10"/>
+      <c r="E95" s="10" t="s">
+        <v>918</v>
+      </c>
     </row>
     <row r="96" spans="1:5" ht="39.950000000000003" customHeight="1">
       <c r="A96" s="22" t="s">
@@ -7384,7 +7512,9 @@
       <c r="D96" s="16" t="s">
         <v>811</v>
       </c>
-      <c r="E96" s="25"/>
+      <c r="E96" s="14" t="s">
+        <v>916</v>
+      </c>
     </row>
     <row r="97" spans="1:5" ht="39.950000000000003" customHeight="1">
       <c r="A97" s="19" t="s">
@@ -7399,7 +7529,9 @@
       <c r="D97" s="10" t="s">
         <v>814</v>
       </c>
-      <c r="E97" s="10"/>
+      <c r="E97" s="14" t="s">
+        <v>916</v>
+      </c>
     </row>
     <row r="98" spans="1:5" ht="39.950000000000003" customHeight="1">
       <c r="A98" s="21" t="s">
@@ -7414,7 +7546,9 @@
       <c r="D98" s="14" t="s">
         <v>817</v>
       </c>
-      <c r="E98" s="14"/>
+      <c r="E98" s="14" t="s">
+        <v>916</v>
+      </c>
     </row>
     <row r="99" spans="1:5" ht="39.950000000000003" customHeight="1">
       <c r="A99" s="19" t="s">
@@ -7429,7 +7563,9 @@
       <c r="D99" s="10" t="s">
         <v>820</v>
       </c>
-      <c r="E99" s="10"/>
+      <c r="E99" s="14" t="s">
+        <v>914</v>
+      </c>
     </row>
     <row r="100" spans="1:5" ht="39.950000000000003" customHeight="1">
       <c r="A100" s="21" t="s">
@@ -7444,7 +7580,9 @@
       <c r="D100" s="14" t="s">
         <v>823</v>
       </c>
-      <c r="E100" s="14"/>
+      <c r="E100" s="14" t="s">
+        <v>917</v>
+      </c>
     </row>
     <row r="101" spans="1:5" ht="39.950000000000003" customHeight="1">
       <c r="A101" s="20" t="s">
@@ -7459,7 +7597,9 @@
       <c r="D101" s="12" t="s">
         <v>826</v>
       </c>
-      <c r="E101" s="24"/>
+      <c r="E101" s="14" t="s">
+        <v>916</v>
+      </c>
     </row>
     <row r="102" spans="1:5" ht="39.950000000000003" customHeight="1">
       <c r="A102" s="21" t="s">
@@ -7474,7 +7614,9 @@
       <c r="D102" s="14" t="s">
         <v>829</v>
       </c>
-      <c r="E102" s="14"/>
+      <c r="E102" s="14" t="s">
+        <v>916</v>
+      </c>
     </row>
     <row r="103" spans="1:5" ht="39.950000000000003" customHeight="1">
       <c r="A103" s="19" t="s">
@@ -7489,7 +7631,9 @@
       <c r="D103" s="10" t="s">
         <v>832</v>
       </c>
-      <c r="E103" s="10"/>
+      <c r="E103" s="14" t="s">
+        <v>914</v>
+      </c>
     </row>
     <row r="104" spans="1:5" ht="39.950000000000003" customHeight="1">
       <c r="A104" s="21" t="s">
@@ -7504,7 +7648,9 @@
       <c r="D104" s="14" t="s">
         <v>835</v>
       </c>
-      <c r="E104" s="14"/>
+      <c r="E104" s="14" t="s">
+        <v>916</v>
+      </c>
     </row>
     <row r="105" spans="1:5" ht="39.950000000000003" customHeight="1">
       <c r="A105" s="19" t="s">
@@ -7519,7 +7665,9 @@
       <c r="D105" s="10" t="s">
         <v>838</v>
       </c>
-      <c r="E105" s="10"/>
+      <c r="E105" s="14" t="s">
+        <v>916</v>
+      </c>
     </row>
     <row r="106" spans="1:5" ht="36.950000000000003" customHeight="1">
       <c r="A106" s="22" t="s">
@@ -7534,7 +7682,9 @@
       <c r="D106" s="16" t="s">
         <v>841</v>
       </c>
-      <c r="E106" s="25"/>
+      <c r="E106" s="14" t="s">
+        <v>914</v>
+      </c>
     </row>
     <row r="107" spans="1:5" ht="36.950000000000003" customHeight="1">
       <c r="A107" s="19" t="s">
@@ -7549,7 +7699,9 @@
       <c r="D107" s="10" t="s">
         <v>844</v>
       </c>
-      <c r="E107" s="10"/>
+      <c r="E107" s="14" t="s">
+        <v>914</v>
+      </c>
     </row>
     <row r="108" spans="1:5" ht="36.950000000000003" customHeight="1">
       <c r="A108" s="21" t="s">
@@ -7564,7 +7716,9 @@
       <c r="D108" s="14" t="s">
         <v>847</v>
       </c>
-      <c r="E108" s="14"/>
+      <c r="E108" s="14" t="s">
+        <v>914</v>
+      </c>
     </row>
     <row r="109" spans="1:5" ht="36.950000000000003" customHeight="1">
       <c r="A109" s="19" t="s">
@@ -7579,7 +7733,9 @@
       <c r="D109" s="10" t="s">
         <v>850</v>
       </c>
-      <c r="E109" s="10"/>
+      <c r="E109" s="14" t="s">
+        <v>914</v>
+      </c>
     </row>
     <row r="110" spans="1:5" ht="36.950000000000003" customHeight="1">
       <c r="A110" s="21" t="s">
@@ -7594,7 +7750,9 @@
       <c r="D110" s="14" t="s">
         <v>853</v>
       </c>
-      <c r="E110" s="14"/>
+      <c r="E110" s="14" t="s">
+        <v>916</v>
+      </c>
     </row>
     <row r="111" spans="1:5" ht="36.950000000000003" customHeight="1">
       <c r="A111" s="19" t="s">
@@ -7609,7 +7767,9 @@
       <c r="D111" s="10" t="s">
         <v>856</v>
       </c>
-      <c r="E111" s="10"/>
+      <c r="E111" s="14" t="s">
+        <v>914</v>
+      </c>
     </row>
     <row r="112" spans="1:5" ht="36.950000000000003" customHeight="1">
       <c r="A112" s="21" t="s">
@@ -7624,7 +7784,9 @@
       <c r="D112" s="14" t="s">
         <v>859</v>
       </c>
-      <c r="E112" s="14"/>
+      <c r="E112" s="14" t="s">
+        <v>916</v>
+      </c>
     </row>
     <row r="113" spans="1:5" ht="36.950000000000003" customHeight="1">
       <c r="A113" s="19" t="s">
@@ -7639,7 +7801,9 @@
       <c r="D113" s="10" t="s">
         <v>862</v>
       </c>
-      <c r="E113" s="10"/>
+      <c r="E113" s="14" t="s">
+        <v>914</v>
+      </c>
     </row>
     <row r="114" spans="1:5" ht="36.950000000000003" customHeight="1">
       <c r="A114" s="21" t="s">
@@ -7654,7 +7818,9 @@
       <c r="D114" s="14" t="s">
         <v>865</v>
       </c>
-      <c r="E114" s="14"/>
+      <c r="E114" s="14" t="s">
+        <v>914</v>
+      </c>
     </row>
     <row r="115" spans="1:5" ht="36.950000000000003" customHeight="1">
       <c r="A115" s="19" t="s">
@@ -7669,7 +7835,9 @@
       <c r="D115" s="10" t="s">
         <v>868</v>
       </c>
-      <c r="E115" s="10"/>
+      <c r="E115" s="14" t="s">
+        <v>916</v>
+      </c>
     </row>
     <row r="116" spans="1:5" ht="39.950000000000003" customHeight="1">
       <c r="A116" s="22" t="s">
@@ -7684,7 +7852,9 @@
       <c r="D116" s="16" t="s">
         <v>871</v>
       </c>
-      <c r="E116" s="25"/>
+      <c r="E116" s="14" t="s">
+        <v>916</v>
+      </c>
     </row>
     <row r="117" spans="1:5" ht="39.950000000000003" customHeight="1">
       <c r="A117" s="19" t="s">
@@ -7699,7 +7869,9 @@
       <c r="D117" s="10" t="s">
         <v>874</v>
       </c>
-      <c r="E117" s="10"/>
+      <c r="E117" s="14" t="s">
+        <v>914</v>
+      </c>
     </row>
     <row r="118" spans="1:5" ht="39.950000000000003" customHeight="1">
       <c r="A118" s="21" t="s">
@@ -7714,7 +7886,9 @@
       <c r="D118" s="14" t="s">
         <v>877</v>
       </c>
-      <c r="E118" s="14"/>
+      <c r="E118" s="14" t="s">
+        <v>914</v>
+      </c>
     </row>
     <row r="119" spans="1:5" ht="39.950000000000003" customHeight="1">
       <c r="A119" s="19" t="s">
@@ -7729,7 +7903,9 @@
       <c r="D119" s="10" t="s">
         <v>880</v>
       </c>
-      <c r="E119" s="10"/>
+      <c r="E119" s="14" t="s">
+        <v>914</v>
+      </c>
     </row>
     <row r="120" spans="1:5" ht="39.950000000000003" customHeight="1">
       <c r="A120" s="21" t="s">
@@ -7744,7 +7920,9 @@
       <c r="D120" s="14" t="s">
         <v>883</v>
       </c>
-      <c r="E120" s="14"/>
+      <c r="E120" s="14" t="s">
+        <v>916</v>
+      </c>
     </row>
     <row r="121" spans="1:5" ht="39.950000000000003" customHeight="1">
       <c r="A121" s="19" t="s">
@@ -7759,7 +7937,9 @@
       <c r="D121" s="10" t="s">
         <v>886</v>
       </c>
-      <c r="E121" s="10"/>
+      <c r="E121" s="14" t="s">
+        <v>916</v>
+      </c>
     </row>
     <row r="122" spans="1:5" ht="39.950000000000003" customHeight="1">
       <c r="A122" s="21" t="s">
@@ -7774,7 +7954,9 @@
       <c r="D122" s="14" t="s">
         <v>889</v>
       </c>
-      <c r="E122" s="14"/>
+      <c r="E122" s="14" t="s">
+        <v>914</v>
+      </c>
     </row>
     <row r="123" spans="1:5" ht="39.950000000000003" customHeight="1">
       <c r="A123" s="19" t="s">
@@ -7789,7 +7971,9 @@
       <c r="D123" s="10" t="s">
         <v>892</v>
       </c>
-      <c r="E123" s="10"/>
+      <c r="E123" s="10" t="s">
+        <v>914</v>
+      </c>
     </row>
     <row r="124" spans="1:5" ht="39.950000000000003" customHeight="1">
       <c r="A124" s="21" t="s">
@@ -7804,7 +7988,9 @@
       <c r="D124" s="14" t="s">
         <v>895</v>
       </c>
-      <c r="E124" s="14"/>
+      <c r="E124" s="14" t="s">
+        <v>914</v>
+      </c>
     </row>
     <row r="125" spans="1:5" ht="39.950000000000003" customHeight="1">
       <c r="A125" s="20" t="s">
@@ -7819,7 +8005,9 @@
       <c r="D125" s="12" t="s">
         <v>898</v>
       </c>
-      <c r="E125" s="24"/>
+      <c r="E125" s="14" t="s">
+        <v>916</v>
+      </c>
     </row>
     <row r="126" spans="1:5" ht="39.950000000000003" customHeight="1">
       <c r="A126" s="21" t="s">
@@ -7834,7 +8022,9 @@
       <c r="D126" s="14" t="s">
         <v>901</v>
       </c>
-      <c r="E126" s="14"/>
+      <c r="E126" s="14" t="s">
+        <v>916</v>
+      </c>
     </row>
     <row r="127" spans="1:5" ht="39.950000000000003" customHeight="1">
       <c r="A127" s="19" t="s">
@@ -7849,7 +8039,9 @@
       <c r="D127" s="10" t="s">
         <v>904</v>
       </c>
-      <c r="E127" s="10"/>
+      <c r="E127" s="14" t="s">
+        <v>916</v>
+      </c>
     </row>
     <row r="128" spans="1:5" ht="39.950000000000003" customHeight="1">
       <c r="A128" s="21" t="s">
@@ -7864,12 +8056,15 @@
       <c r="D128" s="14" t="s">
         <v>907</v>
       </c>
-      <c r="E128" s="14"/>
+      <c r="E128" s="14" t="s">
+        <v>916</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>